--- a/astro-site/public/dl/plan-negocio-paellero-eventos/plan-financiero-paellero-eventos.xlsx
+++ b/astro-site/public/dl/plan-negocio-paellero-eventos/plan-financiero-paellero-eventos.xlsx
@@ -119,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -177,6 +177,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -568,7 +571,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -860,9 +862,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -916,7 +918,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1142,7 +1143,6 @@
         <v>214950.0</v>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
@@ -1320,7 +1320,6 @@
         <v>25794.0</v>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -1509,7 +1508,6 @@
         <v>3840.0</v>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
@@ -1630,8 +1628,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -1675,7 +1673,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1704,13 +1701,13 @@
           <t>Eventos B2C totales</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>57</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="24" t="n">
         <v>72</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="24" t="n">
         <v>86</v>
       </c>
     </row>
@@ -1720,13 +1717,13 @@
           <t>Eventos B2B totales</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>90</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="24" t="n">
         <v>115</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="24" t="n">
         <v>138</v>
       </c>
     </row>
@@ -1951,8 +1948,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -1994,7 +1991,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2074,8 +2070,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -2121,7 +2117,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2408,8 +2403,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -2453,7 +2448,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2672,8 +2666,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/astro-site/public/dl/plan-negocio-paellero-eventos/plan-financiero-paellero-eventos.xlsx
+++ b/astro-site/public/dl/plan-negocio-paellero-eventos/plan-financiero-paellero-eventos.xlsx
@@ -823,7 +823,7 @@
       </c>
       <c r="B9" s="65">
         <f>IFERROR(IF($B$5="","",$B$5*(1+SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11))),"")</f>
-        <v>17.6065164</v>
+        <v>17.60352</v>
       </c>
       <c r="C9" t="str">
         <f>IFERROR("Precio por invitado sin IVA más el IVA medio ponderado de tus líneas de venta: "&amp;TEXT(SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)*100,"0")&amp;" %. En el servicio de paella todo va al 10 % (art. 91.Uno.2.2.º de la Ley 37/1992, alcohol incluido); el alcohol que sale en la paella para recoger mueve la media. Aquí va redondeado. Compáralo con el rango del sector, que va con IVA.","")</f>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="B11" s="64" t="n">
-        <v>0.8519</v>
+        <v>0.92</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="B12" s="66">
         <f>IFERROR(IF(COUNT(B11)=0,"",1-B11),"")</f>
-        <v>0.1481</v>
+        <v>0.07999999999999996</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Vida útil de obra e instalaciones (años)</t>
+          <t>Vida útil de la furgoneta y su rotulación (años)</t>
         </is>
       </c>
       <c r="B44" s="18" t="n">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>En este plan la «obra» es la furgoneta isoterma y su rotulación: ocho años son el 12,5 % anual, por debajo del 16 % máximo para elementos de transporte de la tabla del art. 12.1 de la Ley del Impuesto sobre Sociedades. Confírmalo con tu asesor</t>
+          <t>La furgoneta isoterma y su rotulación se amortizan en ocho años, el 12,5 % anual, por debajo del 16 % máximo para elementos de transporte de la tabla del art. 12.1 de la Ley del Impuesto sobre Sociedades. Confírmalo con tu asesor</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DATO INFORMATIVO: no entra en ningún cálculo. Es la fiesta más grande que puedes servir con dos paelleros, tres auxiliares y tus paelleras (incluida la de 150 cm, de 90-120 raciones)</t>
+          <t>DATO INFORMATIVO: no entra en ningún cálculo. Es la fiesta más grande que puedes servir con dos paelleros, los dos auxiliares y tus paelleras (incluida la de 150 cm, de 90-120 raciones)</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="25" t="inlineStr">
         <is>
-          <t>Es lo que se compra: obra, equipamiento, lanzamiento y gastos de constitución. El colchón de caja no es inversión, es circulante</t>
+          <t>Es lo que se compra: furgoneta, equipamiento, lanzamiento y gastos de constitución. El colchón de caja no es inversión, es circulante</t>
         </is>
       </c>
       <c r="E27" s="28" t="n"/>
@@ -2265,7 +2265,7 @@
     <row r="31">
       <c r="A31" s="28" t="inlineStr">
         <is>
-          <t>Obra, instalaciones y acondicionamiento</t>
+          <t>Furgoneta, rotulación e imprevistos</t>
         </is>
       </c>
       <c r="B31" s="32">
@@ -2541,19 +2541,19 @@
       </c>
       <c r="B10" s="32">
         <f>IFERROR(IF(B9="","",B9*$E$10),"")</f>
-        <v>134532.048</v>
+        <v>145286.4</v>
       </c>
       <c r="C10" s="32">
         <f>IFERROR(IF(C9="","",C9*$E$10),"")</f>
-        <v>147985.2528</v>
+        <v>159815.04</v>
       </c>
       <c r="D10" s="32">
         <f>IFERROR(IF(D9="","",D9*$E$10),"")</f>
-        <v>156864.36796800004</v>
+        <v>169403.94240000003</v>
       </c>
       <c r="E10" s="68">
         <f>IFERROR(IF('0. Supuestos'!$B$11="","",'0. Supuestos'!$B$11),"")</f>
-        <v>0.8519</v>
+        <v>0.92</v>
       </c>
       <c r="F10" s="28" t="inlineStr">
         <is>
@@ -2574,19 +2574,19 @@
       </c>
       <c r="B11" s="32">
         <f>IFERROR(IF(B9="","",B9*$E$11),"")</f>
-        <v>23387.952</v>
+        <v>12633.599999999993</v>
       </c>
       <c r="C11" s="32">
         <f>IFERROR(IF(C9="","",C9*$E$11),"")</f>
-        <v>25726.7472</v>
+        <v>13896.959999999994</v>
       </c>
       <c r="D11" s="32">
         <f>IFERROR(IF(D9="","",D9*$E$11),"")</f>
-        <v>27270.352032000006</v>
+        <v>14730.777599999996</v>
       </c>
       <c r="E11" s="68">
         <f>IFERROR(IF('0. Supuestos'!$B$12="","",'0. Supuestos'!$B$12),"")</f>
-        <v>0.1481</v>
+        <v>0.07999999999999996</v>
       </c>
       <c r="F11" s="28" t="inlineStr">
         <is>
@@ -2621,19 +2621,19 @@
       </c>
       <c r="B13" s="32">
         <f>IFERROR(IF(B9="","",B9*'0. Supuestos'!$B$11*'0. Supuestos'!$B$13),"")</f>
-        <v>37668.97344000001</v>
+        <v>40680.192</v>
       </c>
       <c r="C13" s="32">
         <f>IFERROR(IF(C9="","",C9*'0. Supuestos'!$B$11*'0. Supuestos'!$B$13),"")</f>
-        <v>41435.870784</v>
+        <v>44748.211200000005</v>
       </c>
       <c r="D13" s="32">
         <f>IFERROR(IF(D9="","",D9*'0. Supuestos'!$B$11*'0. Supuestos'!$B$13),"")</f>
-        <v>43922.023031040015</v>
+        <v>47433.103872000014</v>
       </c>
       <c r="E13" s="68">
         <f>IFERROR(B13/$B$9,"")</f>
-        <v>0.23853200000000005</v>
+        <v>0.2576</v>
       </c>
       <c r="F13" s="28" t="str">
         <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$13,"0%")&amp;" de las ventas de COMIDA, no del total: la bebida tiene su propia línea","")</f>
@@ -2653,19 +2653,19 @@
       </c>
       <c r="B14" s="32">
         <f>IFERROR(IF(B9="","",B9*'0. Supuestos'!$B$12*'0. Supuestos'!$B$14),"")</f>
-        <v>7016.3856000000005</v>
+        <v>3790.0799999999977</v>
       </c>
       <c r="C14" s="32">
         <f>IFERROR(IF(C9="","",C9*'0. Supuestos'!$B$12*'0. Supuestos'!$B$14),"")</f>
-        <v>7718.02416</v>
+        <v>4169.087999999998</v>
       </c>
       <c r="D14" s="32">
         <f>IFERROR(IF(D9="","",D9*'0. Supuestos'!$B$12*'0. Supuestos'!$B$14),"")</f>
-        <v>8181.105609600001</v>
+        <v>4419.233279999999</v>
       </c>
       <c r="E14" s="68">
         <f>IFERROR(B14/$B$9,"")</f>
-        <v>0.044430000000000004</v>
+        <v>0.023999999999999987</v>
       </c>
       <c r="F14" s="28" t="str">
         <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$14,"0%")&amp;" de las ventas de BEBIDA","")</f>
@@ -2811,19 +2811,19 @@
       </c>
       <c r="B19" s="26">
         <f>IFERROR(IF(B9="","",SUM(B13:B18)),"")</f>
-        <v>58108.55904000001</v>
+        <v>57893.472</v>
       </c>
       <c r="C19" s="26">
         <f>IFERROR(IF(C9="","",SUM(C13:C18)),"")</f>
-        <v>63919.414944</v>
+        <v>63682.819200000005</v>
       </c>
       <c r="D19" s="26">
         <f>IFERROR(IF(D9="","",SUM(D13:D18)),"")</f>
-        <v>67754.57984064001</v>
+        <v>67503.78835200002</v>
       </c>
       <c r="E19" s="67">
         <f>IFERROR(B19/$B$9,"")</f>
-        <v>0.36796200000000007</v>
+        <v>0.36660000000000004</v>
       </c>
       <c r="F19" s="28" t="n"/>
       <c r="G19" s="28" t="n"/>
@@ -2837,19 +2837,19 @@
       </c>
       <c r="B20" s="26">
         <f>IFERROR(IF(B9="","",B9-B19),"")</f>
-        <v>99811.44095999999</v>
+        <v>100026.52799999999</v>
       </c>
       <c r="C20" s="26">
         <f>IFERROR(IF(C9="","",C9-C19),"")</f>
-        <v>109792.58505600001</v>
+        <v>110029.1808</v>
       </c>
       <c r="D20" s="26">
         <f>IFERROR(IF(D9="","",D9-D19),"")</f>
-        <v>116380.14015936002</v>
+        <v>116630.93164800001</v>
       </c>
       <c r="E20" s="67">
         <f>IFERROR(B20/$B$9,"")</f>
-        <v>0.632038</v>
+        <v>0.6334</v>
       </c>
       <c r="F20" s="28" t="n"/>
       <c r="G20" s="28" t="n"/>
@@ -3417,15 +3417,15 @@
       </c>
       <c r="B39" s="32">
         <f>IFERROR(IF(B9="","",SUMPRODUCT(B13:B18,G13:G18)),"")</f>
-        <v>7507.493112000001</v>
+        <v>7308.5376</v>
       </c>
       <c r="C39" s="32">
         <f>IFERROR(IF(C9="","",SUMPRODUCT(C13:C18,G13:G18)),"")</f>
-        <v>8258.2424232</v>
+        <v>8039.39136</v>
       </c>
       <c r="D39" s="32">
         <f>IFERROR(IF(D9="","",SUMPRODUCT(D13:D18,G13:G18)),"")</f>
-        <v>8753.736968592002</v>
+        <v>8521.754841600003</v>
       </c>
       <c r="E39" s="28" t="n"/>
       <c r="F39" s="28" t="inlineStr">
@@ -3467,19 +3467,19 @@
       </c>
       <c r="B41" s="26">
         <f>IFERROR(IF(B9="","",B20-B38),"")</f>
-        <v>14363.86095999999</v>
+        <v>14578.94799999999</v>
       </c>
       <c r="C41" s="26">
         <f>IFERROR(IF(C9="","",C20-C38),"")</f>
-        <v>18345.00505600001</v>
+        <v>18581.6008</v>
       </c>
       <c r="D41" s="26">
         <f>IFERROR(IF(D9="","",D20-D38),"")</f>
-        <v>19521.63839846199</v>
+        <v>19772.429887101986</v>
       </c>
       <c r="E41" s="67">
         <f>IFERROR(B41/$B$9,"")</f>
-        <v>0.09095656636271524</v>
+        <v>0.09231856636271524</v>
       </c>
       <c r="F41" s="28" t="n"/>
       <c r="G41" s="28" t="n"/>
@@ -3520,15 +3520,15 @@
       </c>
       <c r="B43" s="32">
         <f>IFERROR(IF(B9="","",MAX(0,B41-B42)),"")</f>
-        <v>14363.86095999999</v>
+        <v>14578.94799999999</v>
       </c>
       <c r="C43" s="32">
         <f>IFERROR(IF(C9="","",MAX(0,C41-C42)),"")</f>
-        <v>18345.00505600001</v>
+        <v>18581.6008</v>
       </c>
       <c r="D43" s="32">
         <f>IFERROR(IF(D9="","",MAX(0,D41-D42)),"")</f>
-        <v>19521.63839846199</v>
+        <v>19772.429887101986</v>
       </c>
       <c r="E43" s="28" t="n"/>
       <c r="F43" s="28" t="n"/>
@@ -3593,15 +3593,15 @@
       </c>
       <c r="B46" s="32">
         <f>IFERROR(IF(B9="","",IF(B45="",0,B43*B45)),"")</f>
-        <v>2154.5791439999985</v>
+        <v>2186.8421999999982</v>
       </c>
       <c r="C46" s="32">
         <f>IFERROR(IF(C9="","",IF(C45="",0,C43*C45)),"")</f>
-        <v>2751.7507584000014</v>
+        <v>2787.24012</v>
       </c>
       <c r="D46" s="32">
         <f>IFERROR(IF(D9="","",IF(D45="",0,D43*D45)),"")</f>
-        <v>4880.409599615497</v>
+        <v>4943.107471775496</v>
       </c>
       <c r="E46" s="28" t="n"/>
       <c r="F46" s="28" t="n"/>
@@ -3639,19 +3639,19 @@
       </c>
       <c r="B48" s="26">
         <f>IFERROR(IF(B9="","",B41-B46),"")</f>
-        <v>12209.281815999992</v>
+        <v>12392.10579999999</v>
       </c>
       <c r="C48" s="26">
         <f>IFERROR(IF(C9="","",C41-C46),"")</f>
-        <v>15593.254297600008</v>
+        <v>15794.36068</v>
       </c>
       <c r="D48" s="26">
         <f>IFERROR(IF(D9="","",D41-D46),"")</f>
-        <v>14641.228798846492</v>
+        <v>14829.32241532649</v>
       </c>
       <c r="E48" s="67">
         <f>IFERROR(B48/$B$9,"")</f>
-        <v>0.07731308140830795</v>
+        <v>0.07847078140830795</v>
       </c>
       <c r="F48" s="28" t="n"/>
       <c r="G48" s="28" t="n"/>
@@ -3713,15 +3713,15 @@
       </c>
       <c r="B51" s="68">
         <f>IFERROR(IF(B9="","",B20/B9),"")</f>
-        <v>0.632038</v>
+        <v>0.6334</v>
       </c>
       <c r="C51" s="68">
         <f>IFERROR(IF(C9="","",C20/C9),"")</f>
-        <v>0.6320380000000001</v>
+        <v>0.6334</v>
       </c>
       <c r="D51" s="68">
         <f>IFERROR(IF(D9="","",D20/D9),"")</f>
-        <v>0.632038</v>
+        <v>0.6334</v>
       </c>
       <c r="E51" s="75" t="n">
         <v>0.6</v>
@@ -3742,15 +3742,15 @@
       </c>
       <c r="B52" s="32">
         <f>IFERROR(IF(B9="","",B13+B14),"")</f>
-        <v>44685.35904000001</v>
+        <v>44470.272</v>
       </c>
       <c r="C52" s="32">
         <f>IFERROR(IF(C9="","",C13+C14),"")</f>
-        <v>49153.894944</v>
+        <v>48917.2992</v>
       </c>
       <c r="D52" s="32">
         <f>IFERROR(IF(D9="","",D13+D14),"")</f>
-        <v>52103.12864064002</v>
+        <v>51852.337152000015</v>
       </c>
       <c r="E52" s="28" t="n"/>
       <c r="F52" s="28" t="n"/>
@@ -3765,15 +3765,15 @@
       </c>
       <c r="B53" s="68">
         <f>IFERROR(IF(B9="","",B52/B9),"")</f>
-        <v>0.28296200000000005</v>
+        <v>0.28159999999999996</v>
       </c>
       <c r="C53" s="68">
         <f>IFERROR(IF(C9="","",C52/C9),"")</f>
-        <v>0.282962</v>
+        <v>0.2816</v>
       </c>
       <c r="D53" s="68">
         <f>IFERROR(IF(D9="","",D52/D9),"")</f>
-        <v>0.28296200000000005</v>
+        <v>0.2816</v>
       </c>
       <c r="E53" s="75" t="n">
         <v>0.32</v>
@@ -3852,15 +3852,15 @@
       </c>
       <c r="B56" s="68">
         <f>IFERROR(IF(B9="","",B48/B9),"")</f>
-        <v>0.07731308140830795</v>
+        <v>0.07847078140830795</v>
       </c>
       <c r="C56" s="68">
         <f>IFERROR(IF(C9="","",C48/C9),"")</f>
-        <v>0.08976498052869121</v>
+        <v>0.09092268052869117</v>
       </c>
       <c r="D56" s="68">
         <f>IFERROR(IF(D9="","",D48/D9),"")</f>
-        <v>0.07951367780528566</v>
+        <v>0.08053517780528564</v>
       </c>
       <c r="E56" s="75" t="n">
         <v>0.04</v>
@@ -4170,15 +4170,15 @@
       </c>
       <c r="B9" s="70">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$19/('PyG 3 Años'!$B$6*'PyG 3 Años'!$B$8)),"")</f>
-        <v>5.887392000000001</v>
+        <v>5.865600000000001</v>
       </c>
       <c r="C9" s="70">
         <f>IFERROR(IF('PyG 3 Años'!$C$9="","",'PyG 3 Años'!$C$19/('PyG 3 Años'!$C$6*'PyG 3 Años'!$C$8)),"")</f>
-        <v>5.887391999999999</v>
+        <v>5.865600000000001</v>
       </c>
       <c r="D9" s="70">
         <f>IFERROR(IF('PyG 3 Años'!$D$9="","",'PyG 3 Años'!$D$19/('PyG 3 Años'!$D$6*'PyG 3 Años'!$D$8)),"")</f>
-        <v>5.887392</v>
+        <v>5.865600000000001</v>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
@@ -4195,15 +4195,15 @@
       </c>
       <c r="B10" s="70">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",B8-B9),"")</f>
-        <v>10.112607999999998</v>
+        <v>10.1344</v>
       </c>
       <c r="C10" s="70">
         <f>IFERROR(IF('PyG 3 Años'!$C$9="","",C8-C9),"")</f>
-        <v>10.112608000000002</v>
+        <v>10.1344</v>
       </c>
       <c r="D10" s="70">
         <f>IFERROR(IF('PyG 3 Años'!$D$9="","",D8-D9),"")</f>
-        <v>10.112608</v>
+        <v>10.1344</v>
       </c>
       <c r="E10" s="28" t="inlineStr">
         <is>
@@ -4282,15 +4282,15 @@
       </c>
       <c r="B14" s="40">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",IF(B10&lt;=0,"",B6/B10)),"")</f>
-        <v>8449.608646948445</v>
+        <v>8431.439453741712</v>
       </c>
       <c r="C14" s="40">
         <f>IFERROR(IF('PyG 3 Años'!$C$9="","",IF(C10&lt;=0,"",C6/C10)),"")</f>
-        <v>9042.92740309918</v>
+        <v>9023.482396589834</v>
       </c>
       <c r="D14" s="40">
         <f>IFERROR(IF('PyG 3 Años'!$D$9="","",IF(D10&lt;=0,"",D6/D10)),"")</f>
-        <v>9577.99429790001</v>
+        <v>9557.398737063668</v>
       </c>
       <c r="E14" s="28" t="n"/>
       <c r="F14" s="28" t="n"/>
@@ -4303,15 +4303,15 @@
       </c>
       <c r="B15" s="44">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",B14/B11),"")</f>
-        <v>80.4724633042709</v>
+        <v>80.29942336896869</v>
       </c>
       <c r="C15" s="44">
         <f>IFERROR(IF('PyG 3 Años'!$C$9="","",C14/C11),"")</f>
-        <v>86.1231181247541</v>
+        <v>85.93792758656984</v>
       </c>
       <c r="D15" s="44">
         <f>IFERROR(IF('PyG 3 Años'!$D$9="","",D14/D11),"")</f>
-        <v>91.21899331333343</v>
+        <v>91.02284511489208</v>
       </c>
       <c r="E15" s="28" t="n"/>
       <c r="F15" s="28" t="n"/>
@@ -4324,15 +4324,15 @@
       </c>
       <c r="B16" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",B14*B8),"")</f>
-        <v>135193.73835117512</v>
+        <v>134903.0312598674</v>
       </c>
       <c r="C16" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$C$9="","",C14*C8),"")</f>
-        <v>144686.83844958688</v>
+        <v>144375.71834543734</v>
       </c>
       <c r="D16" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$D$9="","",D14*D8),"")</f>
-        <v>153247.90876640016</v>
+        <v>152918.37979301868</v>
       </c>
       <c r="E16" s="28" t="n"/>
       <c r="F16" s="28" t="n"/>
@@ -4382,15 +4382,15 @@
       </c>
       <c r="B19" s="40">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",IF(B10&lt;=0,"",B18/B10)),"")</f>
-        <v>8079.081083732309</v>
+        <v>8061.708635933061</v>
       </c>
       <c r="C19" s="40">
         <f>IFERROR(IF('PyG 3 Años'!$C$9="","",IF(C10&lt;=0,"",C18/C10)),"")</f>
-        <v>9568.582322189322</v>
+        <v>9548.006999924055</v>
       </c>
       <c r="D19" s="40">
         <f>IFERROR(IF('PyG 3 Años'!$D$9="","",IF(D10&lt;=0,"",D18/D10)),"")</f>
-        <v>10161.90107834006</v>
+        <v>10140.049942772173</v>
       </c>
       <c r="E19" s="28" t="n"/>
       <c r="F19" s="28" t="n"/>
@@ -4403,15 +4403,15 @@
       </c>
       <c r="B20" s="45">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",B19/B11),"")</f>
-        <v>76.94362936887913</v>
+        <v>76.77817748507677</v>
       </c>
       <c r="C20" s="45">
         <f>IFERROR(IF('PyG 3 Años'!$C$9="","",C19/C11),"")</f>
-        <v>91.12935544942212</v>
+        <v>90.93339999927672</v>
       </c>
       <c r="D20" s="45">
         <f>IFERROR(IF('PyG 3 Años'!$D$9="","",D19/D11),"")</f>
-        <v>96.78001026990535</v>
+        <v>96.57190421687784</v>
       </c>
       <c r="E20" s="28" t="n"/>
       <c r="F20" s="28" t="n"/>
@@ -4424,15 +4424,15 @@
       </c>
       <c r="B21" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",B19*B8),"")</f>
-        <v>129265.29733971694</v>
+        <v>128987.33817492897</v>
       </c>
       <c r="C21" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$C$9="","",C19*C8),"")</f>
-        <v>153097.31715502916</v>
+        <v>152768.11199878488</v>
       </c>
       <c r="D21" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$D$9="","",D19*D8),"")</f>
-        <v>162590.41725344097</v>
+        <v>162240.79908435477</v>
       </c>
       <c r="E21" s="28" t="n"/>
       <c r="F21" s="28" t="n"/>
@@ -4478,15 +4478,15 @@
       </c>
       <c r="B24" s="68">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",B23/B20-1),"")</f>
-        <v>0.22167359105651374</v>
+        <v>0.22430621667557293</v>
       </c>
       <c r="C24" s="68">
         <f>IFERROR(IF('PyG 3 Años'!$C$9="","",C23/C20-1),"")</f>
-        <v>0.13465084318947307</v>
+        <v>0.13709594055454266</v>
       </c>
       <c r="D24" s="68">
         <f>IFERROR(IF('PyG 3 Años'!$D$9="","",D23/D20-1),"")</f>
-        <v>0.1325065960866343</v>
+        <v>0.13494707274131357</v>
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
@@ -4585,115 +4585,115 @@
     <row r="32">
       <c r="A32" s="70">
         <f>IFERROR($B$9*0.85,"")</f>
-        <v>5.004283200000001</v>
+        <v>4.98576</v>
       </c>
       <c r="B32" s="44">
         <f>IFERROR(IF($B$31-$A32&lt;=0,"",$B$6/($B$31-$A32)/$B$11),"")</f>
-        <v>90.46377229110594</v>
+        <v>90.27787990895251</v>
       </c>
       <c r="C32" s="44">
         <f>IFERROR(IF($C$31-$A32&lt;=0,"",$B$6/($C$31-$A32)/$B$11),"")</f>
-        <v>74.00940666191731</v>
+        <v>73.88494132963112</v>
       </c>
       <c r="D32" s="44">
         <f>IFERROR(IF($D$31-$A32&lt;=0,"",$B$6/($D$31-$A32)/$B$11),"")</f>
-        <v>62.6195914172642</v>
+        <v>62.53046479782732</v>
       </c>
       <c r="E32" s="44">
         <f>IFERROR(IF($E$31-$A32&lt;=0,"",$B$6/($E$31-$A32)/$B$11),"")</f>
-        <v>54.267927771913925</v>
+        <v>54.20097695191206</v>
       </c>
       <c r="F32" s="28" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="70">
         <f>IFERROR($B$9*0.925,"")</f>
-        <v>5.445837600000001</v>
+        <v>5.425680000000001</v>
       </c>
       <c r="B33" s="44">
         <f>IFERROR(IF($B$31-$A33&lt;=0,"",$B$6/($B$31-$A33)/$B$11),"")</f>
-        <v>95.13339098992044</v>
+        <v>94.90973933681927</v>
       </c>
       <c r="C33" s="44">
         <f>IFERROR(IF($C$31-$A33&lt;=0,"",$B$6/($C$31-$A33)/$B$11),"")</f>
-        <v>77.10573756099075</v>
+        <v>76.95875254299816</v>
       </c>
       <c r="D33" s="44">
         <f>IFERROR(IF($D$31-$A33&lt;=0,"",$B$6/($D$31-$A33)/$B$11),"")</f>
-        <v>64.82204469415468</v>
+        <v>64.71812998161938</v>
       </c>
       <c r="E33" s="44">
         <f>IFERROR(IF($E$31-$A33&lt;=0,"",$B$6/($E$31-$A33)/$B$11),"")</f>
-        <v>55.914346275981934</v>
+        <v>55.837011688399606</v>
       </c>
       <c r="F33" s="28" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="70">
         <f>IFERROR($B$9*1.0,"")</f>
-        <v>5.887392000000001</v>
+        <v>5.865600000000001</v>
       </c>
       <c r="B34" s="44">
         <f>IFERROR(IF($B$31-$A34&lt;=0,"",$B$6/($B$31-$A34)/$B$11),"")</f>
-        <v>100.31132728100216</v>
+        <v>100.04259394552471</v>
       </c>
       <c r="C34" s="44">
         <f>IFERROR(IF($C$31-$A34&lt;=0,"",$B$6/($C$31-$A34)/$B$11),"")</f>
-        <v>80.4724633042709</v>
+        <v>80.29942336896869</v>
       </c>
       <c r="D34" s="44">
         <f>IFERROR(IF($D$31-$A34&lt;=0,"",$B$6/($D$31-$A34)/$B$11),"")</f>
-        <v>67.18507493930922</v>
+        <v>67.0644181987141</v>
       </c>
       <c r="E34" s="44">
         <f>IFERROR(IF($E$31-$A34&lt;=0,"",$B$6/($E$31-$A34)/$B$11),"")</f>
-        <v>57.66379085924276</v>
+        <v>57.57488653147472</v>
       </c>
       <c r="F34" s="28" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="70">
         <f>IFERROR($B$9*1.075,"")</f>
-        <v>6.328946400000001</v>
+        <v>6.3055200000000005</v>
       </c>
       <c r="B35" s="44">
         <f>IFERROR(IF($B$31-$A35&lt;=0,"",$B$6/($B$31-$A35)/$B$11),"")</f>
-        <v>106.08535914681607</v>
+        <v>105.762374610172</v>
       </c>
       <c r="C35" s="44">
         <f>IFERROR(IF($C$31-$A35&lt;=0,"",$B$6/($C$31-$A35)/$B$11),"")</f>
-        <v>84.1466204044693</v>
+        <v>83.94328279500048</v>
       </c>
       <c r="D35" s="44">
         <f>IFERROR(IF($D$31-$A35&lt;=0,"",$B$6/($D$31-$A35)/$B$11),"")</f>
-        <v>69.7269076195894</v>
+        <v>69.5872305729264</v>
       </c>
       <c r="E35" s="44">
         <f>IFERROR(IF($E$31-$A35&lt;=0,"",$B$6/($E$31-$A35)/$B$11),"")</f>
-        <v>59.52624428233361</v>
+        <v>59.42441598297097</v>
       </c>
       <c r="F35" s="28" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="70">
         <f>IFERROR($B$9*1.15,"")</f>
-        <v>6.770500800000001</v>
+        <v>6.74544</v>
       </c>
       <c r="B36" s="44">
         <f>IFERROR(IF($B$31-$A36&lt;=0,"",$B$6/($B$31-$A36)/$B$11),"")</f>
-        <v>112.56470934950464</v>
+        <v>112.17585576388868</v>
       </c>
       <c r="C36" s="44">
         <f>IFERROR(IF($C$31-$A36&lt;=0,"",$B$6/($C$31-$A36)/$B$11),"")</f>
-        <v>88.17233292468092</v>
+        <v>87.9335674727352</v>
       </c>
       <c r="D36" s="44">
         <f>IFERROR(IF($D$31-$A36&lt;=0,"",$B$6/($D$31-$A36)/$B$11),"")</f>
-        <v>72.46863477139534</v>
+        <v>72.30726711577141</v>
       </c>
       <c r="E36" s="44">
         <f>IFERROR(IF($E$31-$A36&lt;=0,"",$B$6/($E$31-$A36)/$B$11),"")</f>
-        <v>61.5130220643935</v>
+        <v>61.39671752140217</v>
       </c>
       <c r="F36" s="28" t="n"/>
     </row>
@@ -5033,15 +5033,15 @@
       </c>
       <c r="B9" s="32">
         <f>IFERROR(IF(B8="","",B8*'0. Supuestos'!$B$11*'0. Supuestos'!$B$13),"")</f>
-        <v>25850.905500000004</v>
+        <v>27917.4</v>
       </c>
       <c r="C9" s="32">
         <f>IFERROR(IF(C8="","",C8*'0. Supuestos'!$B$11*'0. Supuestos'!$B$13),"")</f>
-        <v>37668.97344000001</v>
+        <v>40680.192</v>
       </c>
       <c r="D9" s="32">
         <f>IFERROR(IF(D8="","",D8*'0. Supuestos'!$B$11*'0. Supuestos'!$B$13),"")</f>
-        <v>50688.05</v>
+        <v>54740.00000000001</v>
       </c>
       <c r="E9" s="28" t="n"/>
       <c r="F9" s="28" t="n"/>
@@ -5054,15 +5054,15 @@
       </c>
       <c r="B10" s="32">
         <f>IFERROR(IF(B8="","",B8*'0. Supuestos'!$B$12*'0. Supuestos'!$B$14),"")</f>
-        <v>4815.101250000001</v>
+        <v>2600.9999999999986</v>
       </c>
       <c r="C10" s="32">
         <f>IFERROR(IF(C8="","",C8*'0. Supuestos'!$B$12*'0. Supuestos'!$B$14),"")</f>
-        <v>7016.3856000000005</v>
+        <v>3790.0799999999977</v>
       </c>
       <c r="D10" s="32">
         <f>IFERROR(IF(D8="","",D8*'0. Supuestos'!$B$12*'0. Supuestos'!$B$14),"")</f>
-        <v>9441.375</v>
+        <v>5099.999999999997</v>
       </c>
       <c r="E10" s="28" t="n"/>
       <c r="F10" s="28" t="n"/>
@@ -5159,15 +5159,15 @@
       </c>
       <c r="B15" s="32">
         <f>IFERROR(IF(B8="","",SUM(B9:B14)),"")</f>
-        <v>39877.88175000001</v>
+        <v>39730.275</v>
       </c>
       <c r="C15" s="32">
         <f>IFERROR(IF(C8="","",SUM(C9:C14)),"")</f>
-        <v>58108.55904000001</v>
+        <v>57893.472</v>
       </c>
       <c r="D15" s="32">
         <f>IFERROR(IF(D8="","",SUM(D9:D14)),"")</f>
-        <v>78191.925</v>
+        <v>77902.5</v>
       </c>
       <c r="E15" s="28" t="n"/>
       <c r="F15" s="28" t="n"/>
@@ -5180,15 +5180,15 @@
       </c>
       <c r="B16" s="32">
         <f>IFERROR(IF(B8="","",B8-B15),"")</f>
-        <v>68497.11825</v>
+        <v>68644.725</v>
       </c>
       <c r="C16" s="32">
         <f>IFERROR(IF(C8="","",C8-C15),"")</f>
-        <v>99811.44095999999</v>
+        <v>100026.52799999999</v>
       </c>
       <c r="D16" s="32">
         <f>IFERROR(IF(D8="","",D8-D15),"")</f>
-        <v>134308.075</v>
+        <v>134597.5</v>
       </c>
       <c r="E16" s="28" t="n"/>
       <c r="F16" s="28" t="n"/>
@@ -5226,15 +5226,15 @@
       </c>
       <c r="B18" s="26">
         <f>IFERROR(IF(B8="","",B16-B17),"")</f>
-        <v>-16950.461750000002</v>
+        <v>-16802.854999999996</v>
       </c>
       <c r="C18" s="26">
         <f>IFERROR(IF(C8="","",C16-C17),"")</f>
-        <v>14363.86095999999</v>
+        <v>14578.94799999999</v>
       </c>
       <c r="D18" s="26">
         <f>IFERROR(IF(D8="","",D16-D17),"")</f>
-        <v>48860.49500000001</v>
+        <v>49149.92</v>
       </c>
       <c r="E18" s="28" t="n"/>
       <c r="F18" s="28" t="n"/>
@@ -5251,11 +5251,11 @@
       </c>
       <c r="C19" s="32">
         <f>IFERROR(IF(C8="","",MAX(0,C18-'0. Supuestos'!$B$42)*'0. Supuestos'!$B$37),"")</f>
-        <v>2154.5791439999985</v>
+        <v>2186.8421999999982</v>
       </c>
       <c r="D19" s="32">
         <f>IFERROR(IF(D8="","",MAX(0,D18-'0. Supuestos'!$B$42)*'0. Supuestos'!$B$37),"")</f>
-        <v>7329.0742500000015</v>
+        <v>7372.487999999999</v>
       </c>
       <c r="E19" s="28" t="inlineStr">
         <is>
@@ -5272,15 +5272,15 @@
       </c>
       <c r="B20" s="26">
         <f>IFERROR(IF(B8="","",B18-B19),"")</f>
-        <v>-16950.461750000002</v>
+        <v>-16802.854999999996</v>
       </c>
       <c r="C20" s="26">
         <f>IFERROR(IF(C8="","",C18-C19),"")</f>
-        <v>12209.281815999992</v>
+        <v>12392.10579999999</v>
       </c>
       <c r="D20" s="26">
         <f>IFERROR(IF(D8="","",D18-D19),"")</f>
-        <v>41531.420750000005</v>
+        <v>41777.432</v>
       </c>
       <c r="E20" s="28" t="n"/>
       <c r="F20" s="28" t="n"/>
@@ -5293,15 +5293,15 @@
       </c>
       <c r="B21" s="44">
         <f>IFERROR(IF(B8="","",IF(B6-B15/(B5*B7)&lt;=0,"",B17/(B6-B15/(B5*B7))/B7)),"")</f>
-        <v>106.03430458915693</v>
+        <v>105.80629902734697</v>
       </c>
       <c r="C21" s="44">
         <f>IFERROR(IF(C8="","",IF(C6-C15/(C5*C7)&lt;=0,"",C17/(C6-C15/(C5*C7))/C7)),"")</f>
-        <v>80.4724633042709</v>
+        <v>80.29942336896869</v>
       </c>
       <c r="D21" s="44">
         <f>IFERROR(IF(D8="","",IF(D6-D15/(D5*D7)&lt;=0,"",D17/(D6-D15/(D5*D7))/D7)),"")</f>
-        <v>63.62058275349416</v>
+        <v>63.48377941640817</v>
       </c>
       <c r="E21" s="28" t="n"/>
       <c r="F21" s="28" t="n"/>
@@ -5376,15 +5376,15 @@
       </c>
       <c r="B25" s="26">
         <f>IFERROR(IF(B8="","",'Inversión Inicial'!$B$25+B20+'PyG 3 Años'!$B$36-'Financiación'!$B$45),"")</f>
-        <v>7221.683249999998</v>
+        <v>7369.2900000000045</v>
       </c>
       <c r="C25" s="26">
         <f>IFERROR(IF(C8="","",'Inversión Inicial'!$B$25+C20+'PyG 3 Años'!$B$36-'Financiación'!$B$45),"")</f>
-        <v>36381.42681599999</v>
+        <v>36564.250799999994</v>
       </c>
       <c r="D25" s="26">
         <f>IFERROR(IF(D8="","",'Inversión Inicial'!$B$25+D20+'PyG 3 Años'!$B$36-'Financiación'!$B$45),"")</f>
-        <v>65703.56575000001</v>
+        <v>65949.577</v>
       </c>
       <c r="E25" s="25" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
       <c r="B26" s="28" t="n"/>
       <c r="C26" s="32">
         <f>IFERROR(IF(C8="","",'Tesorería 12 meses'!$M$22),"")</f>
-        <v>37358.12654623951</v>
+        <v>37724.77995568862</v>
       </c>
       <c r="D26" s="28" t="n"/>
       <c r="E26" s="28" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B18" s="68">
         <f>IFERROR(IF('PyG 3 Años'!$B$53="","",'PyG 3 Años'!$B$53),"")</f>
-        <v>0.28296200000000005</v>
+        <v>0.28159999999999996</v>
       </c>
       <c r="C18" s="68">
         <f>IFERROR(IF('PyG 3 Años'!$E$53="","",'PyG 3 Años'!$E$53),"")</f>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="B21" s="68">
         <f>IFERROR(IF('PyG 3 Años'!$B$56="","",'PyG 3 Años'!$B$56),"")</f>
-        <v>0.07731308140830795</v>
+        <v>0.07847078140830795</v>
       </c>
       <c r="C21" s="68">
         <f>IFERROR(IF('PyG 3 Años'!$E$56="","",'PyG 3 Años'!$E$56),"")</f>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="B22" s="68">
         <f>IFERROR(IF('PyG 3 Años'!$B$51="","",'PyG 3 Años'!$B$51),"")</f>
-        <v>0.632038</v>
+        <v>0.6334</v>
       </c>
       <c r="C22" s="68">
         <f>IFERROR(IF('PyG 3 Años'!$E$51="","",'PyG 3 Años'!$E$51),"")</f>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="B29" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$48="","",'PyG 3 Años'!$B$48),"")</f>
-        <v>12209.281815999992</v>
+        <v>12392.10579999999</v>
       </c>
       <c r="C29" s="28" t="n"/>
       <c r="D29" s="28" t="n"/>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="B30" s="44">
         <f>IFERROR(IF('Punto Equilibrio'!$B$15="","",'Punto Equilibrio'!$B$15),"")</f>
-        <v>80.4724633042709</v>
+        <v>80.29942336896869</v>
       </c>
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="28" t="n"/>
@@ -6560,7 +6560,7 @@
     <row r="33">
       <c r="A33" s="25" t="inlineStr">
         <is>
-          <t>QUÉ HA CAMBIADO RESPECTO DE LA VERSIÓN 1.1</t>
+          <t>QUÉ HA CAMBIADO RESPECTO DE LA VERSIÓN 1.2</t>
         </is>
       </c>
       <c r="B33" s="28" t="n"/>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>v1.1</t>
+          <t>v1.2</t>
         </is>
       </c>
       <c r="C34" s="25" t="inlineStr">
@@ -7575,55 +7575,55 @@
       </c>
       <c r="B9" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",('PyG 3 Años'!$B$9+'PyG 3 Años'!$B$9*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11))*B7*(1-MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>1021.9950200748505</v>
+        <v>1021.8210898203594</v>
       </c>
       <c r="C9" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",('PyG 3 Años'!$B$9+'PyG 3 Años'!$B$9*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11))*(C7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+B7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>3431.425703766467</v>
+        <v>3430.8417197604786</v>
       </c>
       <c r="D9" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",('PyG 3 Años'!$B$9+'PyG 3 Años'!$B$9*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11))*(D7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+C7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>5487.803562341317</v>
+        <v>5486.869609580838</v>
       </c>
       <c r="E9" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",('PyG 3 Años'!$B$9+'PyG 3 Años'!$B$9*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11))*(E7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+D7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>8981.168358233534</v>
+        <v>8979.639880239522</v>
       </c>
       <c r="F9" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",('PyG 3 Años'!$B$9+'PyG 3 Años'!$B$9*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11))*(F7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+E7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>13310.710897823352</v>
+        <v>13308.445588023951</v>
       </c>
       <c r="G9" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",('PyG 3 Años'!$B$9+'PyG 3 Años'!$B$9*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11))*(G7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+F7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>20452.288219922157</v>
+        <v>20448.807506586825</v>
       </c>
       <c r="H9" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",('PyG 3 Años'!$B$9+'PyG 3 Años'!$B$9*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11))*(H7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+G7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>23536.855007784434</v>
+        <v>23532.849341317367</v>
       </c>
       <c r="I9" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",('PyG 3 Años'!$B$9+'PyG 3 Años'!$B$9*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11))*(I7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+H7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>22298.07316526946</v>
+        <v>22294.278323353294</v>
       </c>
       <c r="J9" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",('PyG 3 Años'!$B$9+'PyG 3 Años'!$B$9*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11))*(J7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+I7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>22917.464086526947</v>
+        <v>22913.56383233533</v>
       </c>
       <c r="K9" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",('PyG 3 Años'!$B$9+'PyG 3 Años'!$B$9*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11))*(K7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+J7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>21678.682244011976</v>
+        <v>21674.992814371253</v>
       </c>
       <c r="L9" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",('PyG 3 Años'!$B$9+'PyG 3 Años'!$B$9*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11))*(L7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+K7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>13626.60026766467</v>
+        <v>13624.281197604789</v>
       </c>
       <c r="M9" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",('PyG 3 Años'!$B$9+'PyG 3 Años'!$B$9*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11))*(M7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+L7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>8981.168358233534</v>
+        <v>8979.639880239522</v>
       </c>
       <c r="N9" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(B9:M9)),"")</f>
-        <v>165724.2348916527</v>
+        <v>165696.03078323352</v>
       </c>
       <c r="O9" s="28" t="inlineStr">
         <is>
@@ -7660,55 +7660,55 @@
       </c>
       <c r="B11" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",-('PyG 3 Años'!$B$13*(1+'PyG 3 Años'!$G$13)+'PyG 3 Años'!$B$14*(1+'PyG 3 Años'!$G$14)+'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$G$15)+'PyG 3 Años'!$B$16*(1+'PyG 3 Años'!$G$16)+'PyG 3 Años'!$B$17*(1+'PyG 3 Años'!$G$17)+'PyG 3 Años'!$B$18*(1+'PyG 3 Años'!$G$18))*B7*(1-MIN(30,'0. Supuestos'!$B$59)/30)),"")</f>
-        <v>-385.89423314371277</v>
+        <v>-383.4592095808384</v>
       </c>
       <c r="C11" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",-('PyG 3 Años'!$B$13*(1+'PyG 3 Años'!$G$13)+'PyG 3 Años'!$B$14*(1+'PyG 3 Años'!$G$14)+'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$G$15)+'PyG 3 Años'!$B$16*(1+'PyG 3 Años'!$G$16)+'PyG 3 Años'!$B$17*(1+'PyG 3 Años'!$G$17)+'PyG 3 Años'!$B$18*(1+'PyG 3 Años'!$G$18))*(C7*(1-MIN(30,'0. Supuestos'!$B$59)/30)+B7*MIN(30,'0. Supuestos'!$B$59)/30)),"")</f>
-        <v>-1295.6691221916171</v>
+        <v>-1287.4933461077844</v>
       </c>
       <c r="D11" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",-('PyG 3 Años'!$B$13*(1+'PyG 3 Años'!$G$13)+'PyG 3 Años'!$B$14*(1+'PyG 3 Años'!$G$14)+'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$G$15)+'PyG 3 Años'!$B$16*(1+'PyG 3 Años'!$G$16)+'PyG 3 Años'!$B$17*(1+'PyG 3 Años'!$G$17)+'PyG 3 Años'!$B$18*(1+'PyG 3 Años'!$G$18))*(D7*(1-MIN(30,'0. Supuestos'!$B$59)/30)+C7*MIN(30,'0. Supuestos'!$B$59)/30)),"")</f>
-        <v>-2072.13509433533</v>
+        <v>-2059.0597556886228</v>
       </c>
       <c r="E11" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",-('PyG 3 Años'!$B$13*(1+'PyG 3 Años'!$G$13)+'PyG 3 Años'!$B$14*(1+'PyG 3 Años'!$G$14)+'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$G$15)+'PyG 3 Años'!$B$16*(1+'PyG 3 Años'!$G$16)+'PyG 3 Años'!$B$17*(1+'PyG 3 Años'!$G$17)+'PyG 3 Años'!$B$18*(1+'PyG 3 Años'!$G$18))*(E7*(1-MIN(30,'0. Supuestos'!$B$59)/30)+D7*MIN(30,'0. Supuestos'!$B$59)/30)),"")</f>
-        <v>-3391.1917458083844</v>
+        <v>-3369.7930538922155</v>
       </c>
       <c r="F11" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",-('PyG 3 Años'!$B$13*(1+'PyG 3 Años'!$G$13)+'PyG 3 Años'!$B$14*(1+'PyG 3 Años'!$G$14)+'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$G$15)+'PyG 3 Años'!$B$16*(1+'PyG 3 Años'!$G$16)+'PyG 3 Años'!$B$17*(1+'PyG 3 Años'!$G$17)+'PyG 3 Años'!$B$18*(1+'PyG 3 Años'!$G$18))*(F7*(1-MIN(30,'0. Supuestos'!$B$59)/30)+E7*MIN(30,'0. Supuestos'!$B$59)/30)),"")</f>
-        <v>-5025.98004258084</v>
+        <v>-4994.265705389221</v>
       </c>
       <c r="G11" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",-('PyG 3 Años'!$B$13*(1+'PyG 3 Años'!$G$13)+'PyG 3 Años'!$B$14*(1+'PyG 3 Años'!$G$14)+'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$G$15)+'PyG 3 Años'!$B$16*(1+'PyG 3 Años'!$G$16)+'PyG 3 Años'!$B$17*(1+'PyG 3 Años'!$G$17)+'PyG 3 Años'!$B$18*(1+'PyG 3 Años'!$G$18))*(G7*(1-MIN(30,'0. Supuestos'!$B$59)/30)+F7*MIN(30,'0. Supuestos'!$B$59)/30)),"")</f>
-        <v>-7722.562168730541</v>
+        <v>-7673.832182035928</v>
       </c>
       <c r="H11" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",-('PyG 3 Años'!$B$13*(1+'PyG 3 Años'!$G$13)+'PyG 3 Años'!$B$14*(1+'PyG 3 Años'!$G$14)+'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$G$15)+'PyG 3 Años'!$B$16*(1+'PyG 3 Años'!$G$16)+'PyG 3 Años'!$B$17*(1+'PyG 3 Años'!$G$17)+'PyG 3 Años'!$B$18*(1+'PyG 3 Años'!$G$18))*(H7*(1-MIN(30,'0. Supuestos'!$B$59)/30)+G7*MIN(30,'0. Supuestos'!$B$59)/30)),"")</f>
-        <v>-8887.26112694611</v>
+        <v>-8831.181796407187</v>
       </c>
       <c r="I11" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",-('PyG 3 Años'!$B$13*(1+'PyG 3 Años'!$G$13)+'PyG 3 Años'!$B$14*(1+'PyG 3 Años'!$G$14)+'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$G$15)+'PyG 3 Años'!$B$16*(1+'PyG 3 Años'!$G$16)+'PyG 3 Años'!$B$17*(1+'PyG 3 Años'!$G$17)+'PyG 3 Años'!$B$18*(1+'PyG 3 Años'!$G$18))*(I7*(1-MIN(30,'0. Supuestos'!$B$59)/30)+H7*MIN(30,'0. Supuestos'!$B$59)/30)),"")</f>
-        <v>-8419.510541317368</v>
+        <v>-8366.382754491018</v>
       </c>
       <c r="J11" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",-('PyG 3 Años'!$B$13*(1+'PyG 3 Años'!$G$13)+'PyG 3 Años'!$B$14*(1+'PyG 3 Años'!$G$14)+'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$G$15)+'PyG 3 Años'!$B$16*(1+'PyG 3 Años'!$G$16)+'PyG 3 Años'!$B$17*(1+'PyG 3 Años'!$G$17)+'PyG 3 Años'!$B$18*(1+'PyG 3 Años'!$G$18))*(J7*(1-MIN(30,'0. Supuestos'!$B$59)/30)+I7*MIN(30,'0. Supuestos'!$B$59)/30)),"")</f>
-        <v>-8653.38583413174</v>
+        <v>-8598.782275449103</v>
       </c>
       <c r="K11" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",-('PyG 3 Años'!$B$13*(1+'PyG 3 Años'!$G$13)+'PyG 3 Años'!$B$14*(1+'PyG 3 Años'!$G$14)+'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$G$15)+'PyG 3 Años'!$B$16*(1+'PyG 3 Años'!$G$16)+'PyG 3 Años'!$B$17*(1+'PyG 3 Años'!$G$17)+'PyG 3 Años'!$B$18*(1+'PyG 3 Años'!$G$18))*(K7*(1-MIN(30,'0. Supuestos'!$B$59)/30)+J7*MIN(30,'0. Supuestos'!$B$59)/30)),"")</f>
-        <v>-8185.635248502996</v>
+        <v>-8133.983233532934</v>
       </c>
       <c r="L11" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",-('PyG 3 Años'!$B$13*(1+'PyG 3 Años'!$G$13)+'PyG 3 Años'!$B$14*(1+'PyG 3 Años'!$G$14)+'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$G$15)+'PyG 3 Años'!$B$16*(1+'PyG 3 Años'!$G$16)+'PyG 3 Años'!$B$17*(1+'PyG 3 Años'!$G$17)+'PyG 3 Años'!$B$18*(1+'PyG 3 Años'!$G$18))*(L7*(1-MIN(30,'0. Supuestos'!$B$59)/30)+K7*MIN(30,'0. Supuestos'!$B$59)/30)),"")</f>
-        <v>-5145.256441916169</v>
+        <v>-5112.789461077844</v>
       </c>
       <c r="M11" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",-('PyG 3 Años'!$B$13*(1+'PyG 3 Años'!$G$13)+'PyG 3 Años'!$B$14*(1+'PyG 3 Años'!$G$14)+'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$G$15)+'PyG 3 Años'!$B$16*(1+'PyG 3 Años'!$G$16)+'PyG 3 Años'!$B$17*(1+'PyG 3 Años'!$G$17)+'PyG 3 Años'!$B$18*(1+'PyG 3 Años'!$G$18))*(M7*(1-MIN(30,'0. Supuestos'!$B$59)/30)+L7*MIN(30,'0. Supuestos'!$B$59)/30)),"")</f>
-        <v>-3391.1917458083844</v>
+        <v>-3369.7930538922155</v>
       </c>
       <c r="N11" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(B11:M11)),"")</f>
-        <v>-62575.67334541319</v>
+        <v>-62180.81582754491</v>
       </c>
       <c r="O11" s="28" t="str">
         <f>IFERROR("Materia prima, consumibles, comisiones e imprevistos, cada uno con SU tipo de IVA (la columna del P&amp;L) y con los días de pago a proveedor de Supuestos."&amp;IF('0. Supuestos'!$B$59=0,""," Con "&amp;TEXT('0. Supuestos'!$B$59,"0")&amp;" días de pago, las primeras compras se pagan ya en el año siguiente: la columna «Año» de esta fila recoge "&amp;TEXT(MAX(0,12-ROUNDUP('0. Supuestos'!$B$59/30,0)),"0")&amp;" mensualidades de compra, no el coste del ejercicio."),"")</f>
@@ -7971,59 +7971,59 @@
       </c>
       <c r="B16" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$9*B7*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)),"")</f>
-        <v>279.7575153143713</v>
+        <v>279.2357245508982</v>
       </c>
       <c r="C16" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$9*C7*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)),"")</f>
-        <v>379.7920207904192</v>
+        <v>379.0836502994012</v>
       </c>
       <c r="D16" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$9*D7*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)),"")</f>
-        <v>742.6290406526946</v>
+        <v>741.2439233532934</v>
       </c>
       <c r="E16" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$9*E7*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)),"")</f>
-        <v>973.2170532754493</v>
+        <v>971.4018538922157</v>
       </c>
       <c r="F16" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$9*F7*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)),"")</f>
-        <v>1697.1955929071858</v>
+        <v>1694.0300622754492</v>
       </c>
       <c r="G16" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$9*G7*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)),"")</f>
-        <v>2204.1501206586827</v>
+        <v>2200.0390419161677</v>
       </c>
       <c r="H16" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$9*H7*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)),"")</f>
-        <v>2034.6001113772456</v>
+        <v>2030.8052694610778</v>
       </c>
       <c r="I16" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$9*I7*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)),"")</f>
-        <v>2034.6001113772456</v>
+        <v>2030.8052694610778</v>
       </c>
       <c r="J16" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$9*J7*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)),"")</f>
-        <v>2204.1501206586827</v>
+        <v>2200.0390419161677</v>
       </c>
       <c r="K16" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$9*K7*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)),"")</f>
-        <v>1525.950083532934</v>
+        <v>1523.1039520958084</v>
       </c>
       <c r="L16" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$9*L7*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)),"")</f>
-        <v>678.2000371257485</v>
+        <v>676.9350898203593</v>
       </c>
       <c r="M16" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$9*M7*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)),"")</f>
-        <v>1102.0750603293413</v>
+        <v>1100.0195209580838</v>
       </c>
       <c r="N16" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(B16:M16)),"")</f>
-        <v>15856.316868000002</v>
+        <v>15826.742399999997</v>
       </c>
       <c r="O16" s="28" t="inlineStr">
         <is>
-          <t>Cada línea de venta a SU tipo, leído de la columna de IVA del P&amp;L: en el servicio de paella, alcohol incluido, el reducido (art. 91.Uno.2.2.º de la Ley 37/1992 del IVA); el alcohol que sale por paella para recoger, al general; el pan común y las harinas panificables, al superreducido (art. 91.Dos.1.1.º)</t>
+          <t>Cada línea de venta a SU tipo, leído de la columna de IVA del P&amp;L: en el servicio de paella, alcohol incluido, el reducido (art. 91.Uno.2.2.º de la Ley 37/1992 del IVA); el alcohol que sale por paella para recoger, al general; la carpa o el mobiliario facturados aparte, al general (art. 90)</t>
         </is>
       </c>
     </row>
@@ -8035,55 +8035,55 @@
       </c>
       <c r="B17" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$39*B7+'PyG 3 Años'!$B$40/12),"")</f>
-        <v>508.7068395508982</v>
+        <v>505.19661077844313</v>
       </c>
       <c r="C17" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$39*C7+'PyG 3 Años'!$B$40/12),"")</f>
-        <v>556.0701942994012</v>
+        <v>551.3047928143712</v>
       </c>
       <c r="D17" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$39*D7+'PyG 3 Años'!$B$40/12),"")</f>
-        <v>727.8627013532935</v>
+        <v>718.5446395209581</v>
       </c>
       <c r="E17" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$39*E7+'PyG 3 Años'!$B$40/12),"")</f>
-        <v>837.0392478922156</v>
+        <v>824.8279065868264</v>
       </c>
       <c r="F17" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$39*F7+'PyG 3 Años'!$B$40/12),"")</f>
-        <v>1179.8214932754493</v>
+        <v>1158.5261053892216</v>
       </c>
       <c r="G17" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$39*G7+'PyG 3 Años'!$B$40/12),"")</f>
-        <v>1419.8493419161678</v>
+        <v>1392.192994011976</v>
       </c>
       <c r="H17" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$39*H7+'PyG 3 Años'!$B$40/12),"")</f>
-        <v>1339.572469461078</v>
+        <v>1314.0435329341317</v>
       </c>
       <c r="I17" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$39*I7+'PyG 3 Años'!$B$40/12),"")</f>
-        <v>1339.572469461078</v>
+        <v>1314.0435329341317</v>
       </c>
       <c r="J17" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$39*J7+'PyG 3 Años'!$B$40/12),"")</f>
-        <v>1419.8493419161678</v>
+        <v>1392.192994011976</v>
       </c>
       <c r="K17" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$39*K7+'PyG 3 Años'!$B$40/12),"")</f>
-        <v>1098.7418520958086</v>
+        <v>1079.5951497005988</v>
       </c>
       <c r="L17" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$39*L7+'PyG 3 Años'!$B$40/12),"")</f>
-        <v>697.3574898203593</v>
+        <v>688.8478443113772</v>
       </c>
       <c r="M17" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$39*M7+'PyG 3 Años'!$B$40/12),"")</f>
-        <v>898.0496709580839</v>
+        <v>884.221497005988</v>
       </c>
       <c r="N17" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(B17:M17)),"")</f>
-        <v>12022.493112</v>
+        <v>11823.537600000001</v>
       </c>
       <c r="O17" s="28" t="inlineStr">
         <is>
@@ -8108,13 +8108,13 @@
       <c r="G18" s="28" t="n"/>
       <c r="H18" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",MAX(0,-E19)),"")</f>
-        <v>8766.521158446107</v>
+        <v>8751.542744910179</v>
       </c>
       <c r="I18" s="28" t="n"/>
       <c r="J18" s="28" t="n"/>
       <c r="K18" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",MAX(0,-H19)),"")</f>
-        <v>7328.668474688621</v>
+        <v>7261.61879281437</v>
       </c>
       <c r="L18" s="28" t="n"/>
       <c r="M18" s="28" t="n"/>
@@ -8136,19 +8136,19 @@
       <c r="D19" s="28" t="n"/>
       <c r="E19" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(B16:D16)-SUM(B17:D17)-E18),"")</f>
-        <v>-8766.521158446107</v>
+        <v>-8751.542744910179</v>
       </c>
       <c r="F19" s="28" t="n"/>
       <c r="G19" s="28" t="n"/>
       <c r="H19" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(E16:G16)-SUM(E17:G17)-H18),"")</f>
-        <v>-7328.668474688621</v>
+        <v>-7261.61879281437</v>
       </c>
       <c r="I19" s="28" t="n"/>
       <c r="J19" s="28" t="n"/>
       <c r="K19" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(H16:J16)-SUM(H17:J17)-K18),"")</f>
-        <v>-5154.312412113771</v>
+        <v>-5020.249271856286</v>
       </c>
       <c r="L19" s="28" t="n"/>
       <c r="M19" s="28" t="n"/>
@@ -8204,55 +8204,55 @@
       </c>
       <c r="B21" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(B9:B15)+IF(B20="",0,B20)),"")</f>
-        <v>-5892.619213068862</v>
+        <v>-5890.358119760479</v>
       </c>
       <c r="C21" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(C9:C15)+IF(C20="",0,C20)),"")</f>
-        <v>-4392.96341842515</v>
+        <v>-4385.371626347306</v>
       </c>
       <c r="D21" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(D9:D15)+IF(D20="",0,D20)),"")</f>
-        <v>-3113.051531994013</v>
+        <v>-3100.910146107785</v>
       </c>
       <c r="E21" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(E9:E15)+IF(E20="",0,E20)),"")</f>
-        <v>-938.7433875748511</v>
+        <v>-918.8731736526943</v>
       </c>
       <c r="F21" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(F9:F15)+IF(F20="",0,F20)),"")</f>
-        <v>1756.0108552425127</v>
+        <v>1785.4598826347292</v>
       </c>
       <c r="G21" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(G9:G15)+IF(G20="",0,G20)),"")</f>
-        <v>6201.006051191615</v>
+        <v>6246.255324550898</v>
       </c>
       <c r="H21" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(H9:H15)+IF(H20="",0,H20)),"")</f>
-        <v>4185.403880838323</v>
+        <v>4237.47754491018</v>
       </c>
       <c r="I21" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(I9:I15)+IF(I20="",0,I20)),"")</f>
-        <v>7349.842623952091</v>
+        <v>7399.175568862275</v>
       </c>
       <c r="J21" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(J9:J15)+IF(J20="",0,J20)),"")</f>
-        <v>7735.358252395207</v>
+        <v>7786.061556886228</v>
       </c>
       <c r="K21" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(K9:K15)+IF(K20="",0,K20)),"")</f>
-        <v>6964.326995508979</v>
+        <v>7012.289580838319</v>
       </c>
       <c r="L21" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(L9:L15)+IF(L20="",0,L20)),"")</f>
-        <v>1952.6238257484993</v>
+        <v>1982.7717365269446</v>
       </c>
       <c r="M21" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(M9:M15)+IF(M20="",0,M20)),"")</f>
-        <v>-4874.213387574851</v>
+        <v>-4854.3431736526945</v>
       </c>
       <c r="N21" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(B21:M21)),"")</f>
-        <v>16932.981546239498</v>
+        <v>17299.634955688613</v>
       </c>
       <c r="O21" s="28" t="n"/>
     </row>
@@ -8264,51 +8264,51 @@
       </c>
       <c r="B22" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'Inversión Inicial'!$B$25+B21),"")</f>
-        <v>14532.525786931139</v>
+        <v>14534.78688023952</v>
       </c>
       <c r="C22" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",B22+C21),"")</f>
-        <v>10139.562368505989</v>
+        <v>10149.415253892214</v>
       </c>
       <c r="D22" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",C22+D21),"")</f>
-        <v>7026.510836511976</v>
+        <v>7048.505107784429</v>
       </c>
       <c r="E22" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",D22+E21),"")</f>
-        <v>6087.767448937125</v>
+        <v>6129.631934131735</v>
       </c>
       <c r="F22" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",E22+F21),"")</f>
-        <v>7843.778304179637</v>
+        <v>7915.091816766464</v>
       </c>
       <c r="G22" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",F22+G21),"")</f>
-        <v>14044.784355371252</v>
+        <v>14161.347141317361</v>
       </c>
       <c r="H22" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",G22+H21),"")</f>
-        <v>18230.188236209575</v>
+        <v>18398.82468622754</v>
       </c>
       <c r="I22" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",H22+I21),"")</f>
-        <v>25580.030860161667</v>
+        <v>25798.000255089817</v>
       </c>
       <c r="J22" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",I22+J21),"")</f>
-        <v>33315.38911255688</v>
+        <v>33584.06181197605</v>
       </c>
       <c r="K22" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",J22+K21),"")</f>
-        <v>40279.716108065855</v>
+        <v>40596.351392814366</v>
       </c>
       <c r="L22" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",K22+L21),"")</f>
-        <v>42232.33993381436</v>
+        <v>42579.12312934131</v>
       </c>
       <c r="M22" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",L22+M21),"")</f>
-        <v>37358.12654623951</v>
+        <v>37724.77995568862</v>
       </c>
       <c r="N22" s="28" t="n"/>
       <c r="O22" s="28" t="n"/>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="B23" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",IF(COUNT(B22:M22)=0,"",MIN(B22:M22))),"")</f>
-        <v>6087.767448937125</v>
+        <v>6129.631934131735</v>
       </c>
       <c r="C23" s="28" t="n"/>
       <c r="D23" s="28" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="B26" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$48+'PyG 3 Años'!$B$36+'Financiación'!$B$44),"")</f>
-        <v>19310.28181599999</v>
+        <v>19493.10579999999</v>
       </c>
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="28" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="B27" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$C$48+'PyG 3 Años'!$C$36+'Financiación'!$B$46),"")</f>
-        <v>22694.254297600008</v>
+        <v>22895.360679999998</v>
       </c>
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="28" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="B28" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$D$48+'PyG 3 Años'!$D$36+'Financiación'!$B$48),"")</f>
-        <v>21153.15055974452</v>
+        <v>21341.244176224518</v>
       </c>
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="28" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="B29" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",N21+'Financiación'!$B$44+'Financiación'!$B$45),"")</f>
-        <v>20286.981546239498</v>
+        <v>20653.634955688613</v>
       </c>
       <c r="C29" s="28" t="n"/>
       <c r="D29" s="28" t="inlineStr">
@@ -8543,7 +8543,7 @@
       <c r="C31" s="28" t="n"/>
       <c r="D31" s="25" t="inlineStr">
         <is>
-          <t>Mide cuánto tarda el negocio en devolver la inversión con lo que genera ANTES de pagar al banco, con la MISMA base de flujo en los tres años; si puedes pagar la cuota lo dice el DSCR de la hoja de Financiación. El documento Word del pack sigue en la versión 1.1 y no lee esta celda: las cifras válidas son las de este libro</t>
+          <t>Mide cuánto tarda el negocio en devolver la inversión con lo que genera ANTES de pagar al banco, con la MISMA base de flujo en los tres años; si puedes pagar la cuota lo dice el DSCR de la hoja de Financiación. El plan de negocio en Word cita esta cifra; si cambias una celda verde, manda este libro</t>
         </is>
       </c>
       <c r="E31" s="28" t="n"/>
@@ -8571,7 +8571,7 @@
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="28" t="inlineStr">
         <is>
-          <t>El mismo cálculo sobre lo que se COMPRA (obra, equipamiento, lanzamiento y constitución), sin el fondo de maniobra: ese dinero no se gasta, se inmoviliza y vuelve al cerrar el negocio. Informativo: el payback que se publica es el de arriba</t>
+          <t>El mismo cálculo sobre lo que se COMPRA (furgoneta, equipamiento, lanzamiento y constitución), sin el fondo de maniobra: ese dinero no se gasta, se inmoviliza y vuelve al cerrar el negocio. Informativo: el payback que se publica es el de arriba</t>
         </is>
       </c>
       <c r="E32" s="28" t="n"/>
@@ -9841,11 +9841,11 @@
       </c>
       <c r="G27" s="70">
         <f>IFERROR(IF(E27="","",'PyG 3 Años'!$B$41-'PyG 3 Años'!$B$46+'PyG 3 Años'!$B$36+'PyG 3 Años'!$B$37),"")</f>
-        <v>19310.28181599999</v>
+        <v>19493.10579999999</v>
       </c>
       <c r="H27" s="61">
         <f>IFERROR(IF(OR(E27="",E27=0),"",G27/E27),"")</f>
-        <v>5.757388734645197</v>
+        <v>5.811897972570063</v>
       </c>
     </row>
     <row r="28">
@@ -9874,11 +9874,11 @@
       </c>
       <c r="G28" s="70">
         <f>IFERROR(IF(E28="","",'PyG 3 Años'!$C$41-'PyG 3 Años'!$C$46+'PyG 3 Años'!$C$36+'PyG 3 Años'!$C$37),"")</f>
-        <v>22694.254297600008</v>
+        <v>22895.360679999998</v>
       </c>
       <c r="H28" s="61">
         <f>IFERROR(IF(OR(E28="",E28=0),"",G28/E28),"")</f>
-        <v>1.8277140687681694</v>
+        <v>1.843910457493328</v>
       </c>
     </row>
     <row r="29">
@@ -9907,11 +9907,11 @@
       </c>
       <c r="G29" s="70">
         <f>IFERROR(IF(E29="","",'PyG 3 Años'!$D$41-'PyG 3 Años'!$D$46+'PyG 3 Años'!$D$36+'PyG 3 Años'!$D$37),"")</f>
-        <v>21153.15055974452</v>
+        <v>21341.244176224518</v>
       </c>
       <c r="H29" s="61">
         <f>IFERROR(IF(OR(E29="",E29=0),"",G29/E29),"")</f>
-        <v>1.7035990859106995</v>
+        <v>1.718747473012466</v>
       </c>
     </row>
     <row r="30">
@@ -9940,11 +9940,11 @@
       </c>
       <c r="G30" s="70">
         <f>IFERROR(IF(E30="","",'PyG 3 Años'!$D$41-'PyG 3 Años'!$D$46+'PyG 3 Años'!$D$36+'PyG 3 Años'!$D$37),"")</f>
-        <v>21153.15055974452</v>
+        <v>21341.244176224518</v>
       </c>
       <c r="H30" s="61">
         <f>IFERROR(IF(OR(E30="",E30=0),"",G30/E30),"")</f>
-        <v>1.7035990859106995</v>
+        <v>1.718747473012466</v>
       </c>
     </row>
     <row r="31">
@@ -9973,11 +9973,11 @@
       </c>
       <c r="G31" s="70">
         <f>IFERROR(IF(E31="","",'PyG 3 Años'!$D$41-'PyG 3 Años'!$D$46+'PyG 3 Años'!$D$36+'PyG 3 Años'!$D$37),"")</f>
-        <v>21153.15055974452</v>
+        <v>21341.244176224518</v>
       </c>
       <c r="H31" s="61">
         <f>IFERROR(IF(OR(E31="",E31=0),"",G31/E31),"")</f>
-        <v>1.7035990859106995</v>
+        <v>1.718747473012466</v>
       </c>
     </row>
     <row r="32">
@@ -10006,11 +10006,11 @@
       </c>
       <c r="G32" s="70">
         <f>IFERROR(IF(E32="","",'PyG 3 Años'!$D$41-'PyG 3 Años'!$D$46+'PyG 3 Años'!$D$36+'PyG 3 Años'!$D$37),"")</f>
-        <v>21153.15055974452</v>
+        <v>21341.244176224518</v>
       </c>
       <c r="H32" s="61">
         <f>IFERROR(IF(OR(E32="",E32=0),"",G32/E32),"")</f>
-        <v>1.703599085910706</v>
+        <v>1.7187474730124725</v>
       </c>
     </row>
     <row r="33">
@@ -10475,7 +10475,7 @@
       </c>
       <c r="B51" s="61">
         <f>IFERROR(('PyG 3 Años'!$B$41-'PyG 3 Años'!$B$46+'PyG 3 Años'!$B$36+B44)/(B44+B45),"")</f>
-        <v>5.757388734645197</v>
+        <v>5.811897972570063</v>
       </c>
       <c r="C51" s="28" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
       </c>
       <c r="B52" s="61">
         <f>IFERROR(('PyG 3 Años'!$C$41-'PyG 3 Años'!$C$46+'PyG 3 Años'!$C$36+B46)/(B46+B47),"")</f>
-        <v>1.8277140687681694</v>
+        <v>1.843910457493328</v>
       </c>
       <c r="C52" s="28" t="n"/>
       <c r="D52" s="28" t="n"/>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="B53" s="61">
         <f>IFERROR(('PyG 3 Años'!$D$41-'PyG 3 Años'!$D$46+'PyG 3 Años'!$D$36+B48)/(B48+B49),"")</f>
-        <v>1.7035990859106995</v>
+        <v>1.718747473012466</v>
       </c>
       <c r="C53" s="28" t="n"/>
       <c r="D53" s="28" t="n"/>
@@ -10530,7 +10530,7 @@
       </c>
       <c r="B54" s="62">
         <f>IFERROR(IF(COUNT(H27:H41)=0,"",MIN(H27:H41)),"")</f>
-        <v>1.7035990859106995</v>
+        <v>1.718747473012466</v>
       </c>
       <c r="C54" s="25" t="inlineStr">
         <is>

--- a/astro-site/public/dl/plan-negocio-paellero-eventos/plan-financiero-paellero-eventos.xlsx
+++ b/astro-site/public/dl/plan-negocio-paellero-eventos/plan-financiero-paellero-eventos.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
         <v>0.024338015100185552</v>
       </c>
       <c r="D23" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de la furgoneta de este bloque (Furgoneta isoterma usada con certificado ATP y Rotulación, estanterías y anclajes de botellas), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una compra así sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de la furgoneta de este bloque (Furgoneta isoterma usada con certificado ATP y Rotulación, estanterías y anclajes de botellas), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una "&amp;"compra así sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
         <v>Al 8% de las partidas de la furgoneta de este bloque (Furgoneta isoterma usada con certificado ATP y Rotulación, estanterías y anclajes de botellas), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una compra así sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E23" s="28" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
       <c r="E28" s="28" t="n"/>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="25" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Marca, web, fotos, dossier y lanzamiento, Constitución SL + notaría + registro, Declaración responsable, plan APPCC, alérgenos y formación, Stock inicial de producto, Fianza de la cocina de apoyo, Cuota de la cocina de apoyo de los meses previos al arranque ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B26-B31-B32,"0")&amp;" € de los "&amp;TEXT(B26,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Marca, web, fotos, dossier y lanzamiento, Constitución SL + notaría + registro, Declaración responsable, plan APPCC, alérgenos y formación, Stock inicial de producto, Fianza de la cocina de apoyo, "&amp;"Cuota de la cocina de apoyo de los meses previos al arranque ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B26-B31-B32,"0")&amp;" € de los "&amp;TEXT(B26,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Marca, web, fotos, dossier y lanzamiento, Constitución SL + notaría + registro, Declaración responsable, plan APPCC, alérgenos y formación, Stock inicial de producto, Fianza de la cocina de apoyo, Cuota de la cocina de apoyo de los meses previos al arranque ni Colchón operativo hasta alcanzar el equilibrio. Suman 30825 € de los 63111 € de inversión.</v>
       </c>
       <c r="E33" s="28" t="n"/>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F24" s="28" t="n"/>

--- a/astro-site/public/dl/plan-negocio-paellero-eventos/plan-financiero-paellero-eventos.xlsx
+++ b/astro-site/public/dl/plan-negocio-paellero-eventos/plan-financiero-paellero-eventos.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-negocio-paellero-eventos/plan-financiero-paellero-eventos.xlsx
+++ b/astro-site/public/dl/plan-negocio-paellero-eventos/plan-financiero-paellero-eventos.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
         <v>0.024338015100185552</v>
       </c>
       <c r="D23" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de la furgoneta de este bloque (Furgoneta isoterma usada con certificado ATP y Rotulación, estanterías y anclajes de botellas), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una compra así sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de la furgoneta de este bloque (Furgoneta isoterma usada con certificado ATP y Rotulación, estanterías y anclajes de botellas), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una "&amp;"compra así sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
         <v>Al 8% de las partidas de la furgoneta de este bloque (Furgoneta isoterma usada con certificado ATP y Rotulación, estanterías y anclajes de botellas), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una compra así sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E23" s="28" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
       <c r="E28" s="28" t="n"/>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="25" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Marca, web, fotos, dossier y lanzamiento, Constitución SL + notaría + registro, Declaración responsable, plan APPCC, alérgenos y formación, Stock inicial de producto, Fianza de la cocina de apoyo, Cuota de la cocina de apoyo de los meses previos al arranque ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B26-B31-B32,"0")&amp;" € de los "&amp;TEXT(B26,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Marca, web, fotos, dossier y lanzamiento, Constitución SL + notaría + registro, Declaración responsable, plan APPCC, alérgenos y formación, Stock inicial de producto, Fianza de la cocina de apoyo, "&amp;"Cuota de la cocina de apoyo de los meses previos al arranque ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B26-B31-B32,"0")&amp;" € de los "&amp;TEXT(B26,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Marca, web, fotos, dossier y lanzamiento, Constitución SL + notaría + registro, Declaración responsable, plan APPCC, alérgenos y formación, Stock inicial de producto, Fianza de la cocina de apoyo, Cuota de la cocina de apoyo de los meses previos al arranque ni Colchón operativo hasta alcanzar el equilibrio. Suman 30825 € de los 63111 € de inversión.</v>
       </c>
       <c r="E33" s="28" t="n"/>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F24" s="28" t="n"/>
